--- a/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
+++ b/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
@@ -8434,6 +8434,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="등급 확인" error="S · A · B · C · D 중에서 고르세요." sqref="B5:B200">
+      <formula1>"S,A,B,C,D"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="방향 확인" error="up · down · flat 중에서 고르세요 (비워도 돼요=flat)." sqref="D5:D200">
+      <formula1>"up,down,flat"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
+++ b/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
@@ -8452,7 +8452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8520,6 +8520,11 @@
           <t>국제유가($)</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>S&amp;P 500(p)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -8548,6 +8553,9 @@
       <c r="H5" s="7" t="n">
         <v>42</v>
       </c>
+      <c r="I5" s="7" t="n">
+        <v>3100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -8576,6 +8584,9 @@
       <c r="H6" s="7" t="n">
         <v>68</v>
       </c>
+      <c r="I6" s="7" t="n">
+        <v>4300</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -8604,6 +8615,9 @@
       <c r="H7" s="7" t="n">
         <v>95</v>
       </c>
+      <c r="I7" s="7" t="n">
+        <v>3600</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -8632,6 +8646,9 @@
       <c r="H8" s="7" t="n">
         <v>78</v>
       </c>
+      <c r="I8" s="7" t="n">
+        <v>4200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -8660,6 +8677,9 @@
       <c r="H9" s="7" t="n">
         <v>80</v>
       </c>
+      <c r="I9" s="7" t="n">
+        <v>5100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -8687,6 +8707,9 @@
       </c>
       <c r="H10" s="7" t="n">
         <v>72</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>5400</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
+++ b/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
@@ -8452,7 +8452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8492,37 +8492,42 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
+          <t>코스피지수(pt)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>S&amp;P 500(pt)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>일본지수(pt)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>유럽지수(pt)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
           <t>기준금리(%)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>GDP성장률(%)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>실업률(%)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>환율(원/$)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>물가상승률(%)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>국제유가($)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>S&amp;P 500(p)</t>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>금($/oz)</t>
         </is>
       </c>
     </row>
@@ -8536,25 +8541,28 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0.5</v>
+        <v>2300</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.7</v>
+        <v>3100</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4</v>
+        <v>23000</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1180</v>
+        <v>3300</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="H5" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="I5" s="7" t="n">
-        <v>3100</v>
+      <c r="J5" s="7" t="n">
+        <v>1900</v>
       </c>
     </row>
     <row r="6">
@@ -8567,25 +8575,28 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>4300</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>4300</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>0.75</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="I6" s="7" t="n">
-        <v>4300</v>
+      <c r="J6" s="7" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="7">
@@ -8598,25 +8609,28 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>3.25</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="7" t="n">
         <v>5.1</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="I7" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="I7" s="7" t="n">
-        <v>3600</v>
+      <c r="J7" s="7" t="n">
+        <v>1850</v>
       </c>
     </row>
     <row r="8">
@@ -8629,25 +8643,28 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>1310</v>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <v>3.6</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="I8" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="I8" s="7" t="n">
-        <v>4200</v>
+      <c r="J8" s="7" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -8660,25 +8677,28 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>1350</v>
-      </c>
-      <c r="G9" s="7" t="n">
+      <c r="H9" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="I9" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>5100</v>
+      <c r="J9" s="7" t="n">
+        <v>2600</v>
       </c>
     </row>
     <row r="10">
@@ -8691,25 +8711,28 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>39000</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>1320</v>
-      </c>
-      <c r="G10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="I10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="I10" s="7" t="n">
-        <v>5400</v>
+      <c r="J10" s="7" t="n">
+        <v>2750</v>
       </c>
     </row>
   </sheetData>
